--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,10 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>68</v>
@@ -1457,6 +1461,76 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>249</v>
+      </c>
+      <c r="B79" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>246</v>
+      </c>
+      <c r="B80" t="n">
+        <v>5</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>247</v>
+      </c>
+      <c r="B81" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>191</v>
+      </c>
+      <c r="B82" t="n">
+        <v>10</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>192</v>
+      </c>
+      <c r="B83" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
         <v>1000</v>
       </c>
     </row>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,6 +1534,48 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>251</v>
+      </c>
+      <c r="B84" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>250</v>
+      </c>
+      <c r="B85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>252</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,6 +1534,48 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>250</v>
+      </c>
+      <c r="B84" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>251</v>
+      </c>
+      <c r="B85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>252</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1576,6 +1576,76 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>273</v>
+      </c>
+      <c r="B87" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>269</v>
+      </c>
+      <c r="B88" t="n">
+        <v>10</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>274</v>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>267</v>
+      </c>
+      <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>270</v>
+      </c>
+      <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/MessageLimiter.xlsx
+++ b/data/MessageLimiter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1646,6 +1646,20 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>275</v>
+      </c>
+      <c r="B92" t="n">
+        <v>5</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
